--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.8813,0.0471,0.0247,0.0217</t>
-  </si>
-  <si>
-    <t>0.0727,0.0053,0.0067,0.9682</t>
-  </si>
-  <si>
-    <t>0.4832,0.0175,0.0030,0.6725</t>
-  </si>
-  <si>
-    <t>0.0315,0.0055,0.0031,0.9855</t>
-  </si>
-  <si>
-    <t>0.9924,0.0030,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9764,0.0220,0.0012,0.0023</t>
-  </si>
-  <si>
-    <t>0.9876,0.0032,0.0016,0.0038</t>
-  </si>
-  <si>
-    <t>0.9899,0.0050,0.0003,0.0020</t>
-  </si>
-  <si>
-    <t>0.9878,0.0087,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.9847,0.0050,0.0008,0.0040</t>
-  </si>
-  <si>
-    <t>0.9916,0.0031,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9915,0.0037,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.5665,0.0683,0.4775,0.0237</t>
-  </si>
-  <si>
-    <t>0.1654,0.0539,0.8465,0.0027</t>
-  </si>
-  <si>
-    <t>0.1447,0.0451,0.8523,0.0162</t>
-  </si>
-  <si>
-    <t>0.2070,0.0312,0.8245,0.0078</t>
-  </si>
-  <si>
-    <t>0.7541,0.0275,0.3282,0.0060</t>
-  </si>
-  <si>
-    <t>0.0146,0.9691,0.0514,0.0003</t>
-  </si>
-  <si>
-    <t>0.0021,0.9942,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.1273,0.8938,0.0100,0.0021</t>
-  </si>
-  <si>
-    <t>0.0068,0.9869,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.9972,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.6281,0.0245,0.3531,0.0341</t>
-  </si>
-  <si>
-    <t>0.4585,0.0883,0.4927,0.0536</t>
-  </si>
-  <si>
-    <t>0.0294,0.0095,0.9627,0.0101</t>
-  </si>
-  <si>
-    <t>0.2093,0.2086,0.5022,0.0104</t>
-  </si>
-  <si>
-    <t>0.1310,0.0137,0.9162,0.0067</t>
-  </si>
-  <si>
-    <t>0.0704,0.0164,0.9248,0.0175</t>
-  </si>
-  <si>
-    <t>0.0009,0.0028,0.9952,0.0061</t>
-  </si>
-  <si>
-    <t>0.2094,0.8237,0.0122,0.0037</t>
-  </si>
-  <si>
-    <t>0.7349,0.0668,0.2457,0.0221</t>
-  </si>
-  <si>
-    <t>0.0018,0.0199,0.9910,0.0075</t>
-  </si>
-  <si>
-    <t>0.0138,0.8796,0.2687,0.0006</t>
-  </si>
-  <si>
-    <t>0.9036,0.0968,0.0081,0.0138</t>
-  </si>
-  <si>
-    <t>0.8216,0.1847,0.0413,0.0064</t>
-  </si>
-  <si>
-    <t>0.8934,0.1471,0.0160,0.0015</t>
-  </si>
-  <si>
-    <t>0.0188,0.9607,0.1691,0.0013</t>
-  </si>
-  <si>
-    <t>0.0131,0.8507,0.5587,0.0052</t>
-  </si>
-  <si>
-    <t>0.0155,0.0978,0.9460,0.0155</t>
-  </si>
-  <si>
-    <t>0.1049,0.2877,0.7250,0.0143</t>
-  </si>
-  <si>
-    <t>0.0268,0.0056,0.9413,0.0521</t>
-  </si>
-  <si>
-    <t>0.0139,0.3135,0.8837,0.0026</t>
-  </si>
-  <si>
-    <t>0.0025,0.9798,0.0682,0.0042</t>
-  </si>
-  <si>
-    <t>0.0077,0.2802,0.9197,0.0033</t>
-  </si>
-  <si>
-    <t>0.0586,0.8382,0.0267,0.2123</t>
-  </si>
-  <si>
-    <t>0.0002,0.9963,0.0069,0.0044</t>
-  </si>
-  <si>
-    <t>0.0031,0.9738,0.1688,0.0021</t>
-  </si>
-  <si>
-    <t>0.0001,0.9981,0.0035,0.0018</t>
-  </si>
-  <si>
-    <t>0.0019,0.0246,0.9789,0.0164</t>
-  </si>
-  <si>
-    <t>0.0048,0.1491,0.9787,0.0010</t>
-  </si>
-  <si>
-    <t>0.0817,0.0153,0.9032,0.0394</t>
-  </si>
-  <si>
-    <t>0.0091,0.0037,0.9828,0.0139</t>
-  </si>
-  <si>
-    <t>0.0010,0.0275,0.9939,0.0022</t>
-  </si>
-  <si>
-    <t>0.0133,0.0202,0.9723,0.0027</t>
-  </si>
-  <si>
-    <t>0.9221,0.0960,0.0184,0.0014</t>
-  </si>
-  <si>
-    <t>0.9339,0.0411,0.0281,0.0049</t>
-  </si>
-  <si>
-    <t>0.9411,0.0722,0.0105,0.0026</t>
-  </si>
-  <si>
-    <t>0.0065,0.0255,0.9873,0.0035</t>
-  </si>
-  <si>
-    <t>0.9780,0.0104,0.0018,0.0051</t>
-  </si>
-  <si>
-    <t>0.9823,0.0191,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.9506,0.0425,0.0161,0.0012</t>
-  </si>
-  <si>
-    <t>0.0008,0.4988,0.9886,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.0262,0.9851,0.0028</t>
-  </si>
-  <si>
-    <t>0.0242,0.1485,0.9334,0.0022</t>
-  </si>
-  <si>
-    <t>0.0002,0.8435,0.9844,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0215,0.9947,0.0016</t>
-  </si>
-  <si>
-    <t>0.0118,0.9660,0.0243,0.0004</t>
-  </si>
-  <si>
-    <t>0.0130,0.9825,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.8857,0.0376,0.1275,0.0023</t>
-  </si>
-  <si>
-    <t>0.4518,0.6261,0.0282,0.0030</t>
-  </si>
-  <si>
-    <t>0.0041,0.0273,0.9818,0.0173</t>
-  </si>
-  <si>
-    <t>0.0009,0.9138,0.7489,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9769,0.8232,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.9899,0.1036,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.9810,0.4165,0.0005</t>
-  </si>
-  <si>
-    <t>0.0295,0.0007,0.0490,0.9602</t>
-  </si>
-  <si>
-    <t>0.0036,0.0030,0.0007,0.9976</t>
-  </si>
-  <si>
-    <t>0.0125,0.0048,0.0003,0.9950</t>
-  </si>
-  <si>
-    <t>0.0935,0.0217,0.0062,0.9577</t>
-  </si>
-  <si>
-    <t>0.0143,0.0059,0.0085,0.9886</t>
-  </si>
-  <si>
-    <t>0.0010,0.0254,0.0004,0.9983</t>
-  </si>
-  <si>
-    <t>0.0012,0.9832,0.4493,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.8662,0.9867,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.8807,0.7502,0.0001</t>
-  </si>
-  <si>
-    <t>0.0098,0.6176,0.8773,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.9711,0.4302,0.0003</t>
-  </si>
-  <si>
-    <t>0.0012,0.8375,0.8809,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0021,0.0001,0.0051</t>
-  </si>
-  <si>
-    <t>0.9847,0.0175,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.9754,0.0197,0.0012,0.0018</t>
-  </si>
-  <si>
-    <t>0.9871,0.0023,0.0012,0.0047</t>
-  </si>
-  <si>
-    <t>0.9472,0.0706,0.0052,0.0009</t>
-  </si>
-  <si>
-    <t>0.9841,0.0048,0.0020,0.0047</t>
-  </si>
-  <si>
-    <t>0.9400,0.0627,0.0107,0.0009</t>
-  </si>
-  <si>
-    <t>0.9898,0.0018,0.0004,0.0042</t>
-  </si>
-  <si>
-    <t>0.9954,0.0016,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9903,0.0030,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.9842,0.0063,0.0005,0.0031</t>
-  </si>
-  <si>
-    <t>0.9917,0.0017,0.0003,0.0028</t>
-  </si>
-  <si>
-    <t>0.9779,0.0121,0.0011,0.0041</t>
-  </si>
-  <si>
-    <t>0.9831,0.0086,0.0035,0.0015</t>
-  </si>
-  <si>
-    <t>0.9932,0.0025,0.0004,0.0014</t>
-  </si>
-  <si>
-    <t>0.9844,0.0168,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9980,0.0193</t>
-  </si>
-  <si>
-    <t>0.0164,0.0086,0.9737,0.0120</t>
-  </si>
-  <si>
-    <t>0.5082,0.0702,0.4726,0.0695</t>
-  </si>
-  <si>
-    <t>0.0112,0.0314,0.9636,0.0196</t>
-  </si>
-  <si>
-    <t>0.0069,0.9815,0.0041,0.0044</t>
-  </si>
-  <si>
-    <t>0.0206,0.9687,0.0228,0.0008</t>
-  </si>
-  <si>
-    <t>0.0785,0.9370,0.0030,0.0011</t>
-  </si>
-  <si>
-    <t>0.1453,0.8739,0.0175,0.0008</t>
-  </si>
-  <si>
-    <t>0.0104,0.9811,0.0087,0.0010</t>
-  </si>
-  <si>
-    <t>0.0079,0.9841,0.0011,0.0016</t>
-  </si>
-  <si>
-    <t>0.8927,0.1291,0.0218,0.0008</t>
-  </si>
-  <si>
-    <t>0.7081,0.0729,0.1781,0.0280</t>
-  </si>
-  <si>
-    <t>0.5397,0.0339,0.4901,0.0331</t>
-  </si>
-  <si>
-    <t>0.7412,0.0287,0.1608,0.0244</t>
-  </si>
-  <si>
-    <t>0.6975,0.0360,0.2781,0.0203</t>
-  </si>
-  <si>
-    <t>0.2861,0.2069,0.0255,0.6277</t>
-  </si>
-  <si>
-    <t>0.0005,0.9965,0.0070,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.9961,0.0098,0.0045</t>
-  </si>
-  <si>
-    <t>0.0096,0.9570,0.0101,0.0567</t>
-  </si>
-  <si>
-    <t>0.0001,0.9866,0.9067,0.0000</t>
-  </si>
-  <si>
-    <t>0.0093,0.9825,0.0491,0.0004</t>
-  </si>
-  <si>
-    <t>0.4476,0.6685,0.0154,0.0042</t>
-  </si>
-  <si>
-    <t>0.5408,0.5292,0.0492,0.0058</t>
-  </si>
-  <si>
-    <t>0.9766,0.0058,0.0010,0.0093</t>
-  </si>
-  <si>
-    <t>0.9871,0.0053,0.0014,0.0024</t>
-  </si>
-  <si>
-    <t>0.9460,0.0145,0.0050,0.0164</t>
-  </si>
-  <si>
-    <t>0.9850,0.0036,0.0026,0.0029</t>
-  </si>
-  <si>
-    <t>0.9945,0.0009,0.0004,0.0020</t>
-  </si>
-  <si>
-    <t>0.9700,0.0292,0.0045,0.0017</t>
-  </si>
-  <si>
-    <t>0.9418,0.0340,0.0098,0.0112</t>
-  </si>
-  <si>
-    <t>0.9699,0.0288,0.0041,0.0024</t>
-  </si>
-  <si>
-    <t>0.0074,0.1979,0.9680,0.0010</t>
-  </si>
-  <si>
-    <t>0.0091,0.5725,0.8793,0.0023</t>
-  </si>
-  <si>
-    <t>0.0138,0.1633,0.9430,0.0028</t>
-  </si>
-  <si>
-    <t>0.0008,0.7541,0.9628,0.0001</t>
-  </si>
-  <si>
-    <t>0.7662,0.0876,0.0967,0.0290</t>
-  </si>
-  <si>
-    <t>0.7137,0.1064,0.0899,0.0740</t>
-  </si>
-  <si>
-    <t>0.6749,0.0088,0.5015,0.0071</t>
-  </si>
-  <si>
-    <t>0.7204,0.0492,0.1977,0.0157</t>
-  </si>
-  <si>
-    <t>0.0414,0.0014,0.0052,0.9806</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.0021,0.9991</t>
-  </si>
-  <si>
-    <t>0.0132,0.0284,0.0073,0.9848</t>
-  </si>
-  <si>
-    <t>0.0043,0.0010,0.0003,0.9984</t>
-  </si>
-  <si>
-    <t>0.0007,0.9748,0.4473,0.0016</t>
-  </si>
-  <si>
-    <t>0.9199,0.0423,0.0121,0.0198</t>
-  </si>
-  <si>
-    <t>0.2458,0.8001,0.0217,0.0043</t>
-  </si>
-  <si>
-    <t>0.9834,0.0031,0.0001,0.0073</t>
-  </si>
-  <si>
-    <t>0.3787,0.7389,0.0084,0.0021</t>
-  </si>
-  <si>
-    <t>0.9280,0.0366,0.0311,0.0049</t>
-  </si>
-  <si>
-    <t>0.9294,0.0123,0.0115,0.0354</t>
-  </si>
-  <si>
-    <t>0.9673,0.0065,0.0026,0.0203</t>
-  </si>
-  <si>
-    <t>0.0000,0.3747,0.9638,0.0032</t>
-  </si>
-  <si>
-    <t>0.7627,0.0041,0.0894,0.0759</t>
-  </si>
-  <si>
-    <t>0.9546,0.0124,0.0059,0.0142</t>
-  </si>
-  <si>
-    <t>0.7513,0.2127,0.0594,0.0057</t>
-  </si>
-  <si>
-    <t>0.6759,0.3978,0.0192,0.0077</t>
-  </si>
-  <si>
-    <t>0.8137,0.2665,0.0145,0.0030</t>
-  </si>
-  <si>
-    <t>0.5044,0.4691,0.0246,0.0375</t>
-  </si>
-  <si>
-    <t>0.7945,0.1589,0.0625,0.0131</t>
-  </si>
-  <si>
-    <t>0.9304,0.0377,0.0242,0.0021</t>
-  </si>
-  <si>
-    <t>0.9946,0.0014,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9723,0.0079,0.0013,0.0180</t>
-  </si>
-  <si>
-    <t>0.9876,0.0033,0.0004,0.0044</t>
-  </si>
-  <si>
-    <t>0.9645,0.0051,0.0050,0.0185</t>
-  </si>
-  <si>
-    <t>0.9578,0.0182,0.0076,0.0098</t>
-  </si>
-  <si>
-    <t>0.9890,0.0014,0.0005,0.0053</t>
-  </si>
-  <si>
-    <t>0.9838,0.0070,0.0011,0.0027</t>
-  </si>
-  <si>
-    <t>0.9786,0.0043,0.0003,0.0083</t>
-  </si>
-  <si>
-    <t>0.6836,0.4228,0.0281,0.0056</t>
-  </si>
-  <si>
-    <t>0.8575,0.1751,0.0303,0.0015</t>
-  </si>
-  <si>
-    <t>0.7618,0.3444,0.0044,0.0033</t>
-  </si>
-  <si>
-    <t>0.0697,0.7491,0.4901,0.0010</t>
-  </si>
-  <si>
-    <t>0.9486,0.0434,0.0111,0.0032</t>
-  </si>
-  <si>
-    <t>0.8790,0.1906,0.0106,0.0011</t>
-  </si>
-  <si>
-    <t>0.9155,0.1359,0.0049,0.0011</t>
-  </si>
-  <si>
-    <t>0.9461,0.0486,0.0042,0.0048</t>
-  </si>
-  <si>
-    <t>0.0053,0.0336,0.9908,0.0016</t>
-  </si>
-  <si>
-    <t>0.8543,0.1348,0.0459,0.0024</t>
-  </si>
-  <si>
-    <t>0.0109,0.0356,0.9713,0.0016</t>
-  </si>
-  <si>
-    <t>0.0260,0.0690,0.9471,0.0068</t>
-  </si>
-  <si>
-    <t>0.0386,0.0057,0.9717,0.0023</t>
-  </si>
-  <si>
-    <t>0.0010,0.4194,0.9794,0.0007</t>
-  </si>
-  <si>
-    <t>0.0072,0.0579,0.9746,0.0017</t>
-  </si>
-  <si>
-    <t>0.0044,0.0295,0.9836,0.0041</t>
-  </si>
-  <si>
-    <t>0.0059,0.0133,0.9874,0.0024</t>
-  </si>
-  <si>
-    <t>0.1916,0.0209,0.8865,0.0064</t>
-  </si>
-  <si>
-    <t>0.3348,0.0148,0.8146,0.0075</t>
-  </si>
-  <si>
-    <t>0.5914,0.0714,0.3732,0.0421</t>
-  </si>
-  <si>
-    <t>0.3232,0.2487,0.4857,0.0046</t>
-  </si>
-  <si>
-    <t>0.0431,0.8299,0.3315,0.0115</t>
-  </si>
-  <si>
-    <t>0.2623,0.1605,0.5518,0.0031</t>
-  </si>
-  <si>
-    <t>0.5712,0.0600,0.4109,0.0310</t>
-  </si>
-  <si>
-    <t>0.2959,0.1071,0.6637,0.0061</t>
-  </si>
-  <si>
-    <t>0.5583,0.5061,0.0550,0.0035</t>
-  </si>
-  <si>
-    <t>0.2921,0.8234,0.0034,0.0013</t>
-  </si>
-  <si>
-    <t>0.5704,0.5511,0.0160,0.0018</t>
-  </si>
-  <si>
-    <t>0.9681,0.0569,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.6786,0.4877,0.0068,0.0010</t>
-  </si>
-  <si>
-    <t>0.6101,0.0767,0.3497,0.0251</t>
-  </si>
-  <si>
-    <t>0.7056,0.0207,0.4022,0.0061</t>
-  </si>
-  <si>
-    <t>0.1761,0.0196,0.0225,0.8993</t>
-  </si>
-  <si>
-    <t>0.5467,0.0246,0.5289,0.0127</t>
-  </si>
-  <si>
-    <t>0.8038,0.0138,0.0253,0.1023</t>
-  </si>
-  <si>
-    <t>0.0017,0.0074,0.9910,0.0105</t>
-  </si>
-  <si>
-    <t>0.0155,0.4162,0.8169,0.0047</t>
-  </si>
-  <si>
-    <t>0.0174,0.0608,0.9575,0.0015</t>
-  </si>
-  <si>
-    <t>0.0230,0.3819,0.8727,0.0047</t>
-  </si>
-  <si>
-    <t>0.0195,0.3874,0.7829,0.0037</t>
-  </si>
-  <si>
-    <t>0.9883,0.0058,0.0008,0.0020</t>
-  </si>
-  <si>
-    <t>0.9819,0.0069,0.0050,0.0023</t>
-  </si>
-  <si>
-    <t>0.9818,0.0151,0.0013,0.0018</t>
-  </si>
-  <si>
-    <t>0.9868,0.0149,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9736,0.0244,0.0060,0.0008</t>
-  </si>
-  <si>
-    <t>0.9894,0.0053,0.0016,0.0011</t>
-  </si>
-  <si>
-    <t>0.9874,0.0059,0.0021,0.0018</t>
-  </si>
-  <si>
-    <t>0.9642,0.0525,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.0748,0.0084,0.9684,0.0018</t>
-  </si>
-  <si>
-    <t>0.0600,0.4174,0.7108,0.0027</t>
-  </si>
-  <si>
-    <t>0.8916,0.0073,0.0890,0.0104</t>
-  </si>
-  <si>
-    <t>0.0152,0.0169,0.9719,0.0072</t>
-  </si>
-  <si>
-    <t>0.0038,0.1686,0.9693,0.0026</t>
-  </si>
-  <si>
-    <t>0.0390,0.1825,0.8476,0.0011</t>
-  </si>
-  <si>
-    <t>0.0085,0.0195,0.9851,0.0026</t>
-  </si>
-  <si>
-    <t>0.0137,0.0083,0.9814,0.0013</t>
-  </si>
-  <si>
-    <t>0.0068,0.0785,0.9776,0.0017</t>
-  </si>
-  <si>
-    <t>0.0065,0.0335,0.9776,0.0030</t>
-  </si>
-  <si>
-    <t>0.1661,0.1637,0.7129,0.0187</t>
-  </si>
-  <si>
-    <t>0.5347,0.0102,0.6594,0.0091</t>
-  </si>
-  <si>
-    <t>0.6665,0.0124,0.4574,0.0082</t>
-  </si>
-  <si>
-    <t>0.7109,0.0337,0.0364,0.1998</t>
-  </si>
-  <si>
-    <t>0.9712,0.0141,0.0064,0.0032</t>
-  </si>
-  <si>
-    <t>0.9383,0.0899,0.0062,0.0012</t>
-  </si>
-  <si>
-    <t>0.9890,0.0059,0.0007,0.0018</t>
-  </si>
-  <si>
-    <t>0.9900,0.0109,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9889,0.0063,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.9723,0.0324,0.0036,0.0008</t>
-  </si>
-  <si>
-    <t>0.9942,0.0021,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9895,0.0044,0.0004,0.0019</t>
-  </si>
-  <si>
-    <t>0.0219,0.1434,0.9188,0.0017</t>
-  </si>
-  <si>
-    <t>0.0067,0.1926,0.9523,0.0037</t>
-  </si>
-  <si>
-    <t>0.0126,0.0337,0.9621,0.0088</t>
-  </si>
-  <si>
-    <t>0.1220,0.1793,0.6775,0.0088</t>
-  </si>
-  <si>
-    <t>0.0019,0.0221,0.9872,0.0039</t>
-  </si>
-  <si>
-    <t>0.0147,0.0059,0.5581,0.7960</t>
-  </si>
-  <si>
-    <t>0.2157,0.0288,0.8274,0.0034</t>
-  </si>
-  <si>
-    <t>0.0454,0.0259,0.9058,0.0416</t>
-  </si>
-  <si>
-    <t>0.3221,0.0005,0.0129,0.7708</t>
-  </si>
-  <si>
-    <t>0.1174,0.0273,0.0012,0.9346</t>
-  </si>
-  <si>
-    <t>0.2558,0.0148,0.0025,0.8857</t>
-  </si>
-  <si>
-    <t>0.0057,0.0006,0.0016,0.9963</t>
-  </si>
-  <si>
-    <t>0.0059,0.0004,0.0005,0.9976</t>
-  </si>
-  <si>
-    <t>0.6828,0.1285,0.0094,0.0998</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.7937,0.0658,0.0919,0.0309</t>
+  </si>
+  <si>
+    <t>0.0808,0.0044,0.0024,0.9734</t>
+  </si>
+  <si>
+    <t>0.8947,0.0237,0.0045,0.0715</t>
+  </si>
+  <si>
+    <t>0.2701,0.0135,0.0040,0.8324</t>
+  </si>
+  <si>
+    <t>0.9883,0.0103,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9889,0.0019,0.0001,0.0039</t>
+  </si>
+  <si>
+    <t>0.9871,0.0058,0.0026,0.0014</t>
+  </si>
+  <si>
+    <t>0.9854,0.0048,0.0015,0.0050</t>
+  </si>
+  <si>
+    <t>0.9871,0.0110,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9910,0.0027,0.0001,0.0024</t>
+  </si>
+  <si>
+    <t>0.9872,0.0022,0.0006,0.0061</t>
+  </si>
+  <si>
+    <t>0.9940,0.0021,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.5649,0.1305,0.3493,0.0448</t>
+  </si>
+  <si>
+    <t>0.4672,0.1560,0.4349,0.0096</t>
+  </si>
+  <si>
+    <t>0.2577,0.0225,0.8373,0.0054</t>
+  </si>
+  <si>
+    <t>0.3824,0.0283,0.7517,0.0046</t>
+  </si>
+  <si>
+    <t>0.6849,0.1058,0.2563,0.0044</t>
+  </si>
+  <si>
+    <t>0.0072,0.9868,0.0195,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9973,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.0362,0.9621,0.0016,0.0021</t>
+  </si>
+  <si>
+    <t>0.0074,0.9861,0.0072,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.9964,0.0047,0.0001</t>
+  </si>
+  <si>
+    <t>0.5183,0.0497,0.1787,0.2855</t>
+  </si>
+  <si>
+    <t>0.3896,0.1308,0.2812,0.3689</t>
+  </si>
+  <si>
+    <t>0.0954,0.0257,0.8883,0.0741</t>
+  </si>
+  <si>
+    <t>0.2823,0.0309,0.7148,0.0483</t>
+  </si>
+  <si>
+    <t>0.0484,0.0331,0.9480,0.0088</t>
+  </si>
+  <si>
+    <t>0.1755,0.0227,0.8462,0.0130</t>
+  </si>
+  <si>
+    <t>0.0007,0.0007,0.9962,0.0116</t>
+  </si>
+  <si>
+    <t>0.6478,0.4767,0.0120,0.0010</t>
+  </si>
+  <si>
+    <t>0.3925,0.4903,0.2864,0.0118</t>
+  </si>
+  <si>
+    <t>0.0019,0.0135,0.9949,0.0030</t>
+  </si>
+  <si>
+    <t>0.0307,0.8267,0.2604,0.0004</t>
+  </si>
+  <si>
+    <t>0.9008,0.0356,0.0166,0.0311</t>
+  </si>
+  <si>
+    <t>0.2241,0.0748,0.7454,0.0501</t>
+  </si>
+  <si>
+    <t>0.5929,0.3620,0.0794,0.0010</t>
+  </si>
+  <si>
+    <t>0.0391,0.9217,0.2194,0.0020</t>
+  </si>
+  <si>
+    <t>0.0240,0.8738,0.3594,0.0231</t>
+  </si>
+  <si>
+    <t>0.0851,0.1855,0.7758,0.0360</t>
+  </si>
+  <si>
+    <t>0.0517,0.4367,0.6133,0.0436</t>
+  </si>
+  <si>
+    <t>0.3990,0.0202,0.3525,0.1797</t>
+  </si>
+  <si>
+    <t>0.0264,0.0931,0.9286,0.0196</t>
+  </si>
+  <si>
+    <t>0.0075,0.9503,0.1089,0.0037</t>
+  </si>
+  <si>
+    <t>0.0367,0.0744,0.8913,0.0297</t>
+  </si>
+  <si>
+    <t>0.1183,0.4820,0.0089,0.5650</t>
+  </si>
+  <si>
+    <t>0.0001,0.9980,0.0017,0.0030</t>
+  </si>
+  <si>
+    <t>0.0017,0.9870,0.1661,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9974,0.0441,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0442,0.9907,0.0017</t>
+  </si>
+  <si>
+    <t>0.0030,0.3373,0.9785,0.0004</t>
+  </si>
+  <si>
+    <t>0.0111,0.0070,0.9785,0.0097</t>
+  </si>
+  <si>
+    <t>0.2085,0.0148,0.8611,0.0105</t>
+  </si>
+  <si>
+    <t>0.0020,0.0426,0.9747,0.0093</t>
+  </si>
+  <si>
+    <t>0.0659,0.0936,0.8518,0.0031</t>
+  </si>
+  <si>
+    <t>0.9689,0.0288,0.0089,0.0007</t>
+  </si>
+  <si>
+    <t>0.9834,0.0100,0.0029,0.0019</t>
+  </si>
+  <si>
+    <t>0.9238,0.0884,0.0028,0.0042</t>
+  </si>
+  <si>
+    <t>0.0206,0.2090,0.9395,0.0066</t>
+  </si>
+  <si>
+    <t>0.9890,0.0053,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9837,0.0151,0.0027,0.0006</t>
+  </si>
+  <si>
+    <t>0.9741,0.0179,0.0061,0.0014</t>
+  </si>
+  <si>
+    <t>0.0011,0.6257,0.9797,0.0002</t>
+  </si>
+  <si>
+    <t>0.0084,0.5924,0.9301,0.0017</t>
+  </si>
+  <si>
+    <t>0.0031,0.0296,0.9870,0.0020</t>
+  </si>
+  <si>
+    <t>0.0008,0.9554,0.7726,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0103,0.9921,0.0024</t>
+  </si>
+  <si>
+    <t>0.0720,0.9042,0.0435,0.0015</t>
+  </si>
+  <si>
+    <t>0.0047,0.9901,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.9245,0.0690,0.0110,0.0025</t>
+  </si>
+  <si>
+    <t>0.7609,0.1957,0.1030,0.0080</t>
+  </si>
+  <si>
+    <t>0.0223,0.0453,0.9531,0.0482</t>
+  </si>
+  <si>
+    <t>0.0015,0.9520,0.6512,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9798,0.9343,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9728,0.3664,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9745,0.6851,0.0003</t>
+  </si>
+  <si>
+    <t>0.0907,0.0162,0.0068,0.9572</t>
+  </si>
+  <si>
+    <t>0.0052,0.0026,0.0007,0.9972</t>
+  </si>
+  <si>
+    <t>0.0633,0.0021,0.0037,0.9750</t>
+  </si>
+  <si>
+    <t>0.1090,0.0104,0.0058,0.9558</t>
+  </si>
+  <si>
+    <t>0.1386,0.0196,0.0103,0.9328</t>
+  </si>
+  <si>
+    <t>0.0074,0.0225,0.0031,0.9918</t>
+  </si>
+  <si>
+    <t>0.0003,0.9837,0.7740,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.7368,0.9792,0.0001</t>
+  </si>
+  <si>
+    <t>0.0103,0.6482,0.8482,0.0027</t>
+  </si>
+  <si>
+    <t>0.0038,0.5150,0.9354,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.8294,0.9794,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.7918,0.8629,0.0000</t>
+  </si>
+  <si>
+    <t>0.9862,0.0035,0.0018,0.0039</t>
+  </si>
+  <si>
+    <t>0.9837,0.0182,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.9811,0.0185,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9895,0.0042,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9856,0.0065,0.0009,0.0022</t>
+  </si>
+  <si>
+    <t>0.9815,0.0097,0.0041,0.0026</t>
+  </si>
+  <si>
+    <t>0.9924,0.0046,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9701,0.0181,0.0087,0.0021</t>
+  </si>
+  <si>
+    <t>0.9948,0.0029,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9906,0.0051,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9926,0.0023,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9886,0.0055,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.9944,0.0031,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9890,0.0032,0.0020,0.0020</t>
+  </si>
+  <si>
+    <t>0.9873,0.0078,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.9878,0.0074,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.0038,0.0061,0.9880,0.0134</t>
+  </si>
+  <si>
+    <t>0.1679,0.1015,0.7588,0.0162</t>
+  </si>
+  <si>
+    <t>0.4834,0.0311,0.3972,0.1425</t>
+  </si>
+  <si>
+    <t>0.0242,0.0067,0.9651,0.0107</t>
+  </si>
+  <si>
+    <t>0.1153,0.8939,0.0207,0.0008</t>
+  </si>
+  <si>
+    <t>0.0910,0.9140,0.0099,0.0008</t>
+  </si>
+  <si>
+    <t>0.0163,0.9774,0.0009,0.0021</t>
+  </si>
+  <si>
+    <t>0.0877,0.9209,0.0084,0.0004</t>
+  </si>
+  <si>
+    <t>0.0119,0.9779,0.0056,0.0017</t>
+  </si>
+  <si>
+    <t>0.0084,0.9796,0.0078,0.0022</t>
+  </si>
+  <si>
+    <t>0.2176,0.7598,0.0243,0.0005</t>
+  </si>
+  <si>
+    <t>0.7752,0.0372,0.1411,0.0227</t>
+  </si>
+  <si>
+    <t>0.5327,0.0912,0.4083,0.0332</t>
+  </si>
+  <si>
+    <t>0.0826,0.7945,0.0566,0.1685</t>
+  </si>
+  <si>
+    <t>0.6279,0.0630,0.3881,0.0149</t>
+  </si>
+  <si>
+    <t>0.2054,0.1769,0.0800,0.6646</t>
+  </si>
+  <si>
+    <t>0.0003,0.9976,0.0112,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.9919,0.0250,0.0027</t>
+  </si>
+  <si>
+    <t>0.0456,0.9051,0.0489,0.0200</t>
+  </si>
+  <si>
+    <t>0.0001,0.9951,0.1711,0.0004</t>
+  </si>
+  <si>
+    <t>0.0091,0.9873,0.0131,0.0003</t>
+  </si>
+  <si>
+    <t>0.6790,0.4679,0.0195,0.0031</t>
+  </si>
+  <si>
+    <t>0.6580,0.4053,0.0410,0.0020</t>
+  </si>
+  <si>
+    <t>0.9769,0.0170,0.0035,0.0016</t>
+  </si>
+  <si>
+    <t>0.9787,0.0050,0.0066,0.0053</t>
+  </si>
+  <si>
+    <t>0.9713,0.0163,0.0110,0.0016</t>
+  </si>
+  <si>
+    <t>0.9661,0.0141,0.0082,0.0041</t>
+  </si>
+  <si>
+    <t>0.9860,0.0013,0.0009,0.0080</t>
+  </si>
+  <si>
+    <t>0.9865,0.0058,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.9549,0.0193,0.0155,0.0066</t>
+  </si>
+  <si>
+    <t>0.9276,0.0535,0.0259,0.0038</t>
+  </si>
+  <si>
+    <t>0.0018,0.7821,0.9303,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.5515,0.9483,0.0003</t>
+  </si>
+  <si>
+    <t>0.0046,0.8321,0.7242,0.0002</t>
+  </si>
+  <si>
+    <t>0.0071,0.2091,0.9600,0.0015</t>
+  </si>
+  <si>
+    <t>0.8723,0.0369,0.0329,0.0112</t>
+  </si>
+  <si>
+    <t>0.6620,0.2605,0.0910,0.0201</t>
+  </si>
+  <si>
+    <t>0.2328,0.0077,0.8674,0.0183</t>
+  </si>
+  <si>
+    <t>0.5404,0.0498,0.5597,0.0078</t>
+  </si>
+  <si>
+    <t>0.0279,0.0045,0.0143,0.9770</t>
+  </si>
+  <si>
+    <t>0.0006,0.0013,0.0002,0.9994</t>
+  </si>
+  <si>
+    <t>0.0407,0.0139,0.0006,0.9817</t>
+  </si>
+  <si>
+    <t>0.0168,0.0037,0.0044,0.9908</t>
+  </si>
+  <si>
+    <t>0.0013,0.8209,0.6063,0.0066</t>
+  </si>
+  <si>
+    <t>0.9860,0.0046,0.0013,0.0026</t>
+  </si>
+  <si>
+    <t>0.5952,0.3982,0.0209,0.0514</t>
+  </si>
+  <si>
+    <t>0.9791,0.0043,0.0030,0.0053</t>
+  </si>
+  <si>
+    <t>0.7699,0.3399,0.0031,0.0029</t>
+  </si>
+  <si>
+    <t>0.9537,0.0021,0.0059,0.0253</t>
+  </si>
+  <si>
+    <t>0.7601,0.0529,0.1103,0.0739</t>
+  </si>
+  <si>
+    <t>0.9663,0.0184,0.0095,0.0041</t>
+  </si>
+  <si>
+    <t>0.0000,0.1253,0.9950,0.0009</t>
+  </si>
+  <si>
+    <t>0.8680,0.0052,0.0683,0.0210</t>
+  </si>
+  <si>
+    <t>0.8409,0.0596,0.0229,0.0691</t>
+  </si>
+  <si>
+    <t>0.6429,0.2338,0.1255,0.0213</t>
+  </si>
+  <si>
+    <t>0.8101,0.1694,0.0180,0.0144</t>
+  </si>
+  <si>
+    <t>0.7995,0.2144,0.0226,0.0050</t>
+  </si>
+  <si>
+    <t>0.6178,0.3108,0.0463,0.0365</t>
+  </si>
+  <si>
+    <t>0.7253,0.3993,0.0096,0.0015</t>
+  </si>
+  <si>
+    <t>0.9116,0.0767,0.0187,0.0028</t>
+  </si>
+  <si>
+    <t>0.9878,0.0035,0.0004,0.0041</t>
+  </si>
+  <si>
+    <t>0.9812,0.0076,0.0021,0.0054</t>
+  </si>
+  <si>
+    <t>0.9842,0.0047,0.0042,0.0021</t>
+  </si>
+  <si>
+    <t>0.9770,0.0081,0.0045,0.0047</t>
+  </si>
+  <si>
+    <t>0.9837,0.0148,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9363,0.0389,0.0256,0.0044</t>
+  </si>
+  <si>
+    <t>0.9908,0.0011,0.0009,0.0040</t>
+  </si>
+  <si>
+    <t>0.9859,0.0054,0.0013,0.0027</t>
+  </si>
+  <si>
+    <t>0.5443,0.5079,0.0260,0.0166</t>
+  </si>
+  <si>
+    <t>0.6743,0.4346,0.0196,0.0025</t>
+  </si>
+  <si>
+    <t>0.9273,0.1194,0.0043,0.0016</t>
+  </si>
+  <si>
+    <t>0.3077,0.3769,0.4986,0.0030</t>
+  </si>
+  <si>
+    <t>0.8871,0.1861,0.0063,0.0015</t>
+  </si>
+  <si>
+    <t>0.7158,0.2432,0.0843,0.0018</t>
+  </si>
+  <si>
+    <t>0.9357,0.0364,0.0287,0.0021</t>
+  </si>
+  <si>
+    <t>0.9765,0.0136,0.0027,0.0027</t>
+  </si>
+  <si>
+    <t>0.0009,0.0145,0.9976,0.0004</t>
+  </si>
+  <si>
+    <t>0.9359,0.0492,0.0183,0.0036</t>
+  </si>
+  <si>
+    <t>0.0011,0.0437,0.9940,0.0007</t>
+  </si>
+  <si>
+    <t>0.0172,0.2627,0.9396,0.0039</t>
+  </si>
+  <si>
+    <t>0.0082,0.0021,0.9933,0.0006</t>
+  </si>
+  <si>
+    <t>0.0112,0.3654,0.9394,0.0037</t>
+  </si>
+  <si>
+    <t>0.0075,0.3586,0.8880,0.0021</t>
+  </si>
+  <si>
+    <t>0.0011,0.0020,0.9978,0.0006</t>
+  </si>
+  <si>
+    <t>0.0081,0.0045,0.9898,0.0019</t>
+  </si>
+  <si>
+    <t>0.0917,0.0917,0.8449,0.0063</t>
+  </si>
+  <si>
+    <t>0.1190,0.0440,0.8775,0.0024</t>
+  </si>
+  <si>
+    <t>0.3592,0.1420,0.5810,0.0377</t>
+  </si>
+  <si>
+    <t>0.3531,0.3914,0.2058,0.0015</t>
+  </si>
+  <si>
+    <t>0.1583,0.8038,0.0862,0.0020</t>
+  </si>
+  <si>
+    <t>0.7388,0.0198,0.3341,0.0055</t>
+  </si>
+  <si>
+    <t>0.5911,0.0347,0.4935,0.0145</t>
+  </si>
+  <si>
+    <t>0.4167,0.1439,0.5440,0.0174</t>
+  </si>
+  <si>
+    <t>0.8935,0.1506,0.0172,0.0024</t>
+  </si>
+  <si>
+    <t>0.7139,0.4650,0.0075,0.0008</t>
+  </si>
+  <si>
+    <t>0.6845,0.3895,0.0015,0.0038</t>
+  </si>
+  <si>
+    <t>0.9742,0.0350,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9606,0.0573,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.6674,0.1145,0.2202,0.0130</t>
+  </si>
+  <si>
+    <t>0.6334,0.0245,0.3321,0.0472</t>
+  </si>
+  <si>
+    <t>0.7110,0.0758,0.1283,0.0782</t>
+  </si>
+  <si>
+    <t>0.2206,0.0241,0.8103,0.0179</t>
+  </si>
+  <si>
+    <t>0.5637,0.2804,0.1648,0.0581</t>
+  </si>
+  <si>
+    <t>0.0241,0.0276,0.9399,0.0409</t>
+  </si>
+  <si>
+    <t>0.0428,0.1067,0.8941,0.0024</t>
+  </si>
+  <si>
+    <t>0.0264,0.0832,0.9344,0.0067</t>
+  </si>
+  <si>
+    <t>0.0560,0.1453,0.8483,0.0029</t>
+  </si>
+  <si>
+    <t>0.0059,0.0948,0.9677,0.0006</t>
+  </si>
+  <si>
+    <t>0.9891,0.0063,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9852,0.0110,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9776,0.0101,0.0003,0.0061</t>
+  </si>
+  <si>
+    <t>0.9865,0.0057,0.0004,0.0027</t>
+  </si>
+  <si>
+    <t>0.9806,0.0069,0.0035,0.0036</t>
+  </si>
+  <si>
+    <t>0.9895,0.0238,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9749,0.0298,0.0023,0.0016</t>
+  </si>
+  <si>
+    <t>0.9749,0.0150,0.0037,0.0030</t>
+  </si>
+  <si>
+    <t>0.0412,0.0496,0.9541,0.0022</t>
+  </si>
+  <si>
+    <t>0.5438,0.0708,0.5059,0.0250</t>
+  </si>
+  <si>
+    <t>0.7921,0.1503,0.0691,0.0085</t>
+  </si>
+  <si>
+    <t>0.0036,0.0222,0.9792,0.0055</t>
+  </si>
+  <si>
+    <t>0.0006,0.1653,0.9867,0.0015</t>
+  </si>
+  <si>
+    <t>0.0133,0.0336,0.9598,0.0019</t>
+  </si>
+  <si>
+    <t>0.0095,0.0183,0.9871,0.0016</t>
+  </si>
+  <si>
+    <t>0.0656,0.1968,0.7151,0.0027</t>
+  </si>
+  <si>
+    <t>0.0019,0.0109,0.9876,0.0129</t>
+  </si>
+  <si>
+    <t>0.0234,0.0541,0.9514,0.0036</t>
+  </si>
+  <si>
+    <t>0.0560,0.5452,0.5233,0.0011</t>
+  </si>
+  <si>
+    <t>0.6453,0.0176,0.1592,0.1053</t>
+  </si>
+  <si>
+    <t>0.3047,0.0397,0.7493,0.0049</t>
+  </si>
+  <si>
+    <t>0.6701,0.0266,0.0708,0.1650</t>
+  </si>
+  <si>
+    <t>0.9683,0.0180,0.0057,0.0038</t>
+  </si>
+  <si>
+    <t>0.9839,0.0145,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9895,0.0067,0.0021,0.0006</t>
+  </si>
+  <si>
+    <t>0.9914,0.0160,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9895,0.0032,0.0005,0.0033</t>
+  </si>
+  <si>
+    <t>0.9804,0.0156,0.0031,0.0010</t>
+  </si>
+  <si>
+    <t>0.9850,0.0106,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.9897,0.0066,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0180,0.1326,0.9357,0.0004</t>
+  </si>
+  <si>
+    <t>0.0064,0.0633,0.9801,0.0018</t>
+  </si>
+  <si>
+    <t>0.0118,0.1679,0.9245,0.0011</t>
+  </si>
+  <si>
+    <t>0.0436,0.7102,0.3384,0.0039</t>
+  </si>
+  <si>
+    <t>0.0004,0.0028,0.9971,0.0015</t>
+  </si>
+  <si>
+    <t>0.3670,0.0259,0.6828,0.0290</t>
+  </si>
+  <si>
+    <t>0.2841,0.0177,0.7629,0.0215</t>
+  </si>
+  <si>
+    <t>0.0357,0.1010,0.8733,0.0137</t>
+  </si>
+  <si>
+    <t>0.8215,0.0046,0.0390,0.0855</t>
+  </si>
+  <si>
+    <t>0.0685,0.0342,0.0037,0.9667</t>
+  </si>
+  <si>
+    <t>0.0330,0.0146,0.0129,0.9777</t>
+  </si>
+  <si>
+    <t>0.0076,0.0004,0.0011,0.9964</t>
+  </si>
+  <si>
+    <t>0.0011,0.0013,0.0007,0.9988</t>
+  </si>
+  <si>
+    <t>0.6945,0.0897,0.0968,0.0957</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2144,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2522,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2816,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,10 +2830,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3096,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3152,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,10 +3880,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5168,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,10 +5378,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
